--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CDP.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -629,44 +629,44 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>37</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>75.7%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>22</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>40.9%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -681,28 +681,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>CDP_J._OKEMIRIE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J. Okemirie</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:K3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -740,7 +883,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: B. Gomes (12 L)</t>
+          <t>Maior volume: A. Bah (26 L)</t>
         </is>
       </c>
     </row>
@@ -752,7 +895,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: B. Gomes (9 3PA)</t>
+          <t>Maior volume 3pt: A. Bah (14 3PA)</t>
         </is>
       </c>
     </row>
@@ -764,7 +907,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: B. Gomes (1.2 pts/shot)</t>
+          <t>Mais eficaz: D. Buccilli (1.2 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -776,7 +919,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Paint Non-RA (22 L)</t>
+          <t>Zona mais usada: Restricted Area (37 L)</t>
         </is>
       </c>
     </row>
@@ -788,7 +931,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (65.0%)</t>
+          <t>Zona mais eficaz: Restricted Area (75.7%)</t>
         </is>
       </c>
     </row>
@@ -820,7 +963,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
@@ -928,75 +1071,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="n">
-        <v>14</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1005,112 +1148,116 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1118,20 +1265,20 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1139,46 +1286,46 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1187,46 +1334,46 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1241,17 +1388,17 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
         <v>7</v>
       </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1411,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1272,171 +1419,185 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_J._COSTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>J. Costa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>6</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
@@ -1445,43 +1606,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_J._PEDRO</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Pedro</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1494,15 +1659,15 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1512,45 +1677,41 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_M._RODRIGUES</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1558,30 +1719,20 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>8</v>
       </c>
@@ -1589,32 +1740,32 @@
         <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_J._PEDRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1627,19 +1778,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1648,21 +1799,21 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
         <v>8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1677,13 +1828,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1715,9 +1866,19 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
@@ -1725,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1740,11 +1901,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -1756,7 +1917,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
@@ -1864,12 +2025,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1877,66 +2038,60 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>14</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1950,59 +2105,59 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>58.3%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -2015,8 +2170,393 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CDP_B._GOMES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CDP_M._LAMUT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CDP_J._COSTA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CDP_J._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S3"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2121,38 +2661,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2160,74 +2700,74 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>7</v>
       </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>58.3%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2242,48 +2782,48 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2298,7 +2838,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2310,36 +2850,36 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
         <v>3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2354,7 +2894,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2366,17 +2906,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2395,87 +2935,97 @@
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
         <v>0.9</v>
@@ -2486,27 +3036,29 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2522,17 +3074,17 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2540,23 +3092,23 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_J._PEDRO</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Pedro</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2572,41 +3124,41 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_J._PEDRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2622,29 +3174,29 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -2672,10 +3224,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
@@ -2694,7 +3246,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
@@ -2710,28 +3262,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>CDP_B._GOMES</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H3" t="n">
+        <v>27</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2806,46 +3541,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
@@ -2855,22 +3590,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2880,32 +3615,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -2915,25 +3650,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2946,11 +3681,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -2960,57 +3695,57 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>8.2%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3033,7 +3768,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -3131,12 +3866,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3145,156 +3880,156 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -3302,24 +4037,38 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
@@ -3327,43 +4076,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -3371,27 +4120,27 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -3411,45 +4160,45 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -3457,139 +4206,163 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_J._COSTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>J. Costa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P7" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_J._PEDRO</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Pedro</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3602,102 +4375,92 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_M._RODRIGUES</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>1.2</v>
       </c>
@@ -3705,25 +4468,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_J._PEDRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3732,22 +4495,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -3755,7 +4518,7 @@
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12">
@@ -3782,14 +4545,24 @@
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3816,7 +4589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3892,76 +4665,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3969,7 +4742,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -3982,84 +4755,84 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4069,8 +4842,233 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDP_M._LAMUT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CDP_D._BUCCILLI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D. Buccilli</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CDP.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,7 +451,7 @@
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E2" t="n">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -633,40 +633,40 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -681,11 +681,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -789,11 +789,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -802,50 +802,275 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CDP_M._LAMUT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CDP_M._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>41.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -883,7 +1108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: A. Bah (26 L)</t>
+          <t>Maior volume: A. Bah (39 L)</t>
         </is>
       </c>
     </row>
@@ -895,7 +1120,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: A. Bah (14 3PA)</t>
+          <t>Maior volume 3pt: A. Bah (19 3PA)</t>
         </is>
       </c>
     </row>
@@ -907,7 +1132,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: D. Buccilli (1.2 pts/shot)</t>
+          <t>Mais eficaz: J. Okemirie (1.2 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -919,7 +1144,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (37 L)</t>
+          <t>Zona mais usada: Restricted Area (59 L)</t>
         </is>
       </c>
     </row>
@@ -931,7 +1156,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (75.7%)</t>
+          <t>Zona mais eficaz: Restricted Area (69.5%)</t>
         </is>
       </c>
     </row>
@@ -947,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -963,7 +1188,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
@@ -1080,34 +1305,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1115,31 +1340,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1157,107 +1382,107 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>14</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>35.0%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1265,28 +1490,28 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>7</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1296,263 +1521,267 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>14</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>46.7%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>7</v>
       </c>
-      <c r="E6" t="n">
-        <v>14</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>58.3%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
         <v>8</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>5</v>
-      </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_J._COSTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>J. Costa</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1561,28 +1790,28 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1590,195 +1819,199 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
         <v>6</v>
       </c>
-      <c r="R8" t="n">
-        <v>7</v>
-      </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_M._RODRIGUES</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>3</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>8</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
       <c r="Q10" t="n">
         <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDP_J._PEDRO</t>
+          <t>CDP_J._GOMES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Pedro</t>
+          <t>J. Gomes</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1790,12 +2023,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1803,42 +2036,42 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDP_J._MANJATE</t>
+          <t>CDP_J._PEDRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J. Manjate</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1851,46 +2084,123 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
       <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CDP_J._MANJATE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>J. Manjate</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
-        <v>8</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>12</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S12"/>
+  <autoFilter ref="A1:S13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1901,7 +2211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1917,7 +2227,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
@@ -2025,12 +2335,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2038,17 +2348,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
         <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" t="n">
-        <v>14</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2061,77 +2371,67 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H3" t="n">
         <v>14</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2140,45 +2440,45 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2186,55 +2486,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>7</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -2244,53 +2544,53 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -2298,84 +2598,84 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2384,18 +2684,18 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -2404,33 +2704,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_J._COSTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>J. Costa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2439,7 +2739,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2452,111 +2752,265 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CDP_D._BUCCILLI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D. Buccilli</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>6</v>
       </c>
-      <c r="S8" t="n">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CDP_J._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>3</v>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2567,7 +3021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2670,29 +3124,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2700,55 +3154,55 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2756,11 +3210,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2773,113 +3227,113 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_M._RODRIGUES</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
         <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>87.5%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2894,7 +3348,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2906,17 +3360,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2924,33 +3378,33 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_J._GOMES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>J. Gomes</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2962,11 +3416,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -2976,22 +3430,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -3006,7 +3460,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -3018,119 +3472,129 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>14</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="M9" t="n">
-        <v>8</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3138,57 +3602,63 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDP_J._PEDRO</t>
+          <t>CDP_J._MANJATE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Pedro</t>
+          <t>J. Manjate</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -3196,19 +3666,21 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDP_J._MANJATE</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J. Manjate</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3224,34 +3696,84 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CDP_J._PEDRO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>J. Pedro</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>8</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N12"/>
+  <autoFilter ref="A1:N13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3262,11 +3784,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3356,38 +3878,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3395,11 +3917,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -3412,35 +3934,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -3451,22 +3973,134 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>48.7%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" t="n">
+        <v>31</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3545,25 +4179,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -3576,21 +4210,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3598,34 +4232,34 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3633,14 +4267,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3650,25 +4284,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3685,7 +4319,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -3695,22 +4329,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3738,7 +4372,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3760,7 +4394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3768,7 +4402,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -3880,57 +4514,57 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
@@ -3946,28 +4580,28 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3976,73 +4610,73 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -4050,23 +4684,23 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -4076,113 +4710,113 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>17</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>14</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>42.9%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>15</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>46.7%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -4190,34 +4824,38 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
       <c r="P6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4226,11 +4864,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4239,16 +4877,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -4256,56 +4894,56 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>16</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>10</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>4</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_J._COSTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>J. Costa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4313,12 +4951,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -4326,154 +4964,154 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>13</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>10</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P8" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_M._RODRIGUES</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="P10" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDP_J._PEDRO</t>
+          <t>CDP_J._GOMES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Pedro</t>
+          <t>J. Gomes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4486,12 +5124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4499,74 +5137,88 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDP_J._MANJATE</t>
+          <t>CDP_J._PEDRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J. Manjate</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -4574,11 +5226,81 @@
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CDP_J._MANJATE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>J. Manjate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>2</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1.6</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P12"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4589,11 +5311,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -4679,7 +5401,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -4689,150 +5411,150 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4845,21 +5567,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
@@ -4869,64 +5591,64 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -4935,43 +5657,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>22.9%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -4980,43 +5702,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -5025,50 +5747,365 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CDP_M._LAMUT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CDP_B._GOMES</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CDP_J._COSTA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>CDP_A._BAH</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>A. Bah</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CDP_D._BUCCILLI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D. Buccilli</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="E17" t="n">
         <v>4</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CDP.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,80 +590,80 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="E2" t="n">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>78</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>21.8%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>59</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>69.5%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" t="n">
         <v>8</v>
-      </c>
-      <c r="V2" t="n">
-        <v>7</v>
       </c>
       <c r="W2" t="n">
         <v>11</v>
@@ -681,11 +681,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -771,29 +771,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,17 +861,17 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>12</v>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -892,185 +892,455 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
         <v>9</v>
       </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_M._RODRIGUES</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CDP_M._LAMUT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>38.7%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CDP_M._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>CDP_B._WHITAKER</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>B. Whitaker</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D12" t="n">
+        <v>17</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>15</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CDP_BETINHO_GOMES</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Betinho Gomes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F13" t="n">
         <v>9</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H14" t="n">
         <v>0.8</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>34.3%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K14" t="n">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1108,7 +1378,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: A. Bah (39 L)</t>
+          <t>Maior volume: A. Bah (48 L)</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1390,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: A. Bah (19 3PA)</t>
+          <t>Maior volume 3pt: A. Bah (24 3PA)</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1402,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: J. Okemirie (1.2 pts/shot)</t>
+          <t>Mais eficaz: J. Pedro (1.4 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1414,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (59 L)</t>
+          <t>Zona mais usada: Above the Break 3 (78 L)</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1426,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (69.5%)</t>
+          <t>Zona mais eficaz: Restricted Area (68.5%)</t>
         </is>
       </c>
     </row>
@@ -1175,8 +1445,8 @@
   <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -1305,30 +1575,30 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1340,7 +1610,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1353,18 +1623,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1382,34 +1652,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1417,31 +1687,31 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1459,21 +1729,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1482,7 +1752,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1494,7 +1764,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1507,63 +1777,63 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_M._RODRIGUES</t>
+          <t>CDP_BETINHO_GOMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1571,101 +1841,101 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>42.1%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>86.4%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>11</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>36.4%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>68.8%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>7</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1675,7 +1945,7 @@
         <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1690,30 +1960,30 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1725,24 +1995,24 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>7</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>6</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1752,32 +2022,32 @@
         <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1790,61 +2060,61 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
+        <v>10</v>
+      </c>
+      <c r="S8" t="n">
         <v>6</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_J._COSTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>J. Costa</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
@@ -1854,272 +2124,272 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>9</v>
-      </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDP_J._GOMES</t>
+          <t>CDP_J._PEDRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Gomes</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDP_J._PEDRO</t>
+          <t>CDP_J._GOMES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J. Pedro</t>
+          <t>J. Gomes</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -2134,46 +2404,46 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>4</v>
       </c>
-      <c r="E13" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2193,10 +2463,10 @@
         <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2211,11 +2481,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2335,30 +2605,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_J._PEDRO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2375,250 +2645,244 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_M._RODRIGUES</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>7</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>42.9%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_BETINHO_GOMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>37.5%</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>11</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>68.8%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -2627,30 +2891,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H6" t="n">
         <v>19</v>
@@ -2662,7 +2926,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,31 +2935,31 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -2704,89 +2968,89 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>12</v>
       </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2794,62 +3058,62 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>42</v>
+      </c>
+      <c r="H8" t="n">
+        <v>24</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>40.0%</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>35</v>
-      </c>
-      <c r="F8" t="n">
-        <v>14</v>
-      </c>
-      <c r="G8" t="n">
-        <v>31</v>
-      </c>
-      <c r="H8" t="n">
-        <v>14</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>21.4%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>8</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>62.5%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -2871,55 +3135,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>7</v>
       </c>
-      <c r="G9" t="n">
-        <v>14</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>6.2%</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>6</v>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -2929,74 +3193,74 @@
         <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_J._COSTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>J. Costa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>4</v>
       </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -3006,11 +3270,88 @@
         <v>8</v>
       </c>
       <c r="S10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CDP_J._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10.5%</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3024,8 +3365,8 @@
   <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3124,26 +3465,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I2" t="n">
         <v>0.9</v>
@@ -3154,7 +3495,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -3165,7 +3506,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -3180,26 +3521,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I3" t="n">
         <v>1.2</v>
@@ -3210,11 +3551,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -3236,29 +3577,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H4" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3266,67 +3607,67 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_BETINHO_GOMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
+        <v>26</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>11</v>
       </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>68.8%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -3348,7 +3689,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -3360,11 +3701,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
@@ -3389,18 +3730,18 @@
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_J._GOMES</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Gomes</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3416,51 +3757,51 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_J._GOMES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>J. Gomes</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -3472,17 +3813,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -3490,89 +3831,89 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" t="n">
         <v>4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -3584,17 +3925,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3602,18 +3943,18 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -3628,7 +3969,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -3640,17 +3981,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -3658,18 +3999,18 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -3696,13 +4037,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -3710,11 +4051,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -3746,13 +4087,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -3760,11 +4101,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -3787,8 +4128,8 @@
   <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3887,26 +4228,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I2" t="n">
         <v>1.2</v>
@@ -3917,11 +4258,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -3934,50 +4275,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_BETINHO_GOMES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H3" t="n">
+        <v>26</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>11</v>
       </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>68.8%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H3" t="n">
-        <v>16</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>7</v>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -3990,12 +4331,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4011,17 +4352,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H4" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -4029,15 +4370,15 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -4046,35 +4387,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H5" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="I5" t="n">
         <v>0.9</v>
@@ -4085,7 +4426,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -4093,7 +4434,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -4175,71 +4516,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4249,32 +4590,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -4284,32 +4625,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4319,25 +4660,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -4354,32 +4695,32 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4397,8 +4738,8 @@
   <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -4514,7 +4855,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4527,40 +4868,40 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>9</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>44.4%</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="L2" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4584,57 +4925,57 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4654,7 +4995,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4667,11 +5008,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4680,7 +5021,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4688,15 +5029,15 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -4710,12 +5051,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_M._RODRIGUES</t>
+          <t>CDP_BETINHO_GOMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Rodrigues</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4724,68 +5065,68 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4794,11 +5135,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4807,44 +5148,44 @@
         </is>
       </c>
       <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
@@ -4864,53 +5205,53 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="L7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -4920,59 +5261,59 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -4984,18 +5325,18 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_J._COSTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>J. Costa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5004,114 +5345,114 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="P9" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDP_J._GOMES</t>
+          <t>CDP_J._PEDRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Gomes</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5120,68 +5461,54 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDP_J._PEDRO</t>
+          <t>CDP_J._GOMES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J. Pedro</t>
+          <t>J. Gomes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5190,43 +5517,57 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -5246,11 +5587,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -5272,7 +5613,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -5280,15 +5621,15 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -5296,7 +5637,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -5311,11 +5652,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -5401,13 +5742,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5419,7 +5760,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -5446,25 +5787,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -5477,12 +5818,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5491,13 +5832,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5509,7 +5850,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -5532,81 +5873,81 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="n">
-        <v>12</v>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5626,7 +5967,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -5636,123 +5977,123 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_BETINHO_GOMES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
         <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5761,29 +6102,29 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -5792,76 +6133,76 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>19.6%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35.0%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -5869,25 +6210,25 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5896,7 +6237,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>5</v>
@@ -5906,15 +6247,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -5927,27 +6268,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -5959,11 +6300,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
@@ -5972,43 +6313,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
@@ -6017,12 +6358,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6031,29 +6372,29 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -6062,12 +6403,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_J._COSTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>J. Costa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6076,36 +6417,261 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="n">
-        <v>4</v>
-      </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CDP_J._PEDRO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>J. Pedro</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CDP_BETINHO_GOMES</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Betinho Gomes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CDP_M._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CDP_J._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>J. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K17"/>
+  <autoFilter ref="A1:K22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>